--- a/data/excel/Administration_RevenueManagement_SalesCommissionRule.xlsx
+++ b/data/excel/Administration_RevenueManagement_SalesCommissionRule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kumar.gaurav\git\V12StagingB2C\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209BB6CB-A3DB-4187-AE3F-21742E731CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C06796-509A-49DD-8258-632C75E9DDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,10 +572,10 @@
     <t>9@6C6535C</t>
   </si>
   <si>
-    <t>Ankur@123456</t>
-  </si>
-  <si>
     <t>Test111</t>
+  </si>
+  <si>
+    <t>EE6B4B@E7</t>
   </si>
 </sst>
 </file>
@@ -676,7 +676,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -739,6 +739,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6620,20 +6626,20 @@
       <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="17" t="s">
+      <c r="G2" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" t="s">
         <v>176</v>
-      </c>
-      <c r="I2" t="s">
-        <v>177</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -6791,11 +6797,8 @@
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{2868D419-A3BA-4483-86BC-51DB04DE9D2E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{DD0DCC1C-87C2-45E5-8C37-383DE30F7614}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{2BF19DDB-A80D-471A-B197-6AE139D6B0E9}">
-      <formula1>"Piyush_ql,ankur_ql"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD2" xr:uid="{8A819801-D313-4323-8BC2-51F65639219D}">
       <formula1>"Yes,No"</formula1>
@@ -6827,10 +6830,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BH2" xr:uid="{13106842-2512-49C0-AE1F-EC7109FF3B9A}">
       <formula1>"Base Fare,Net Fare Exclusive Tax,Base Fare + YQ,Base Fare + YQ + YR,Base Fare + YR,Net Fare Inclusive Tax"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{BF064567-4334-4DC8-8CE6-C5E937DF618C}">
-      <formula1>"Password@@12,Ankur@12345,9@6C6535C,Ankur@123456"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{8C9D931E-A1A2-4341-980B-975E6192F426}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{939B497F-DF24-470F-B343-6802418555B3}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{E6885841-6E25-44CF-A14B-FAFA28003C03}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>